--- a/public/templates/essay.xlsx
+++ b/public/templates/essay.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,6 +419,9 @@
         <v>시험일</v>
       </c>
       <c r="G1" t="str">
+        <v>시험시간</v>
+      </c>
+      <c r="H1" t="str">
         <v>출처</v>
       </c>
     </row>
@@ -439,15 +442,18 @@
         <v>4합5</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-11-23</v>
+        <v>2026-11-23(일)</v>
       </c>
       <c r="G2" t="str">
+        <v>14:00~15:40</v>
+      </c>
+      <c r="H2" t="str">
         <v>○○대 입학처</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>